--- a/CP_2569_บันทึกผลจริง_template.xlsx
+++ b/CP_2569_บันทึกผลจริง_template.xlsx
@@ -1251,8 +1251,12 @@
       <c r="M6" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
+      <c r="N6" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="O6" s="12" t="n">
+        <v>69</v>
+      </c>
       <c r="P6" s="12"/>
       <c r="Q6" s="12"/>
       <c r="R6" s="12"/>
@@ -1316,8 +1320,12 @@
       <c r="M7" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
+      <c r="N7" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="O7" s="12" t="n">
+        <v>75</v>
+      </c>
       <c r="P7" s="12"/>
       <c r="Q7" s="12"/>
       <c r="R7" s="12"/>
@@ -1381,8 +1389,12 @@
       <c r="M8" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
+      <c r="N8" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="O8" s="12" t="n">
+        <v>75</v>
+      </c>
       <c r="P8" s="12"/>
       <c r="Q8" s="12"/>
       <c r="R8" s="12"/>
@@ -1487,8 +1499,12 @@
       <c r="M10" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
+      <c r="N10" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="O10" s="12" t="n">
+        <v>75</v>
+      </c>
       <c r="P10" s="12"/>
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
@@ -1552,8 +1568,12 @@
       <c r="M11" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
+      <c r="N11" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="O11" s="12" t="n">
+        <v>100</v>
+      </c>
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
       <c r="R11" s="12"/>
@@ -1617,8 +1637,12 @@
       <c r="M12" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
+      <c r="N12" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="O12" s="12" t="n">
+        <v>75</v>
+      </c>
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
       <c r="R12" s="12"/>
@@ -1723,8 +1747,12 @@
       <c r="M14" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
+      <c r="N14" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="O14" s="12" t="n">
+        <v>69</v>
+      </c>
       <c r="P14" s="12"/>
       <c r="Q14" s="12"/>
       <c r="R14" s="12"/>
@@ -1788,8 +1816,12 @@
       <c r="M15" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
+      <c r="N15" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="O15" s="12" t="n">
+        <v>69</v>
+      </c>
       <c r="P15" s="12"/>
       <c r="Q15" s="12"/>
       <c r="R15" s="12"/>
@@ -1853,8 +1885,12 @@
       <c r="M16" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
+      <c r="N16" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="O16" s="12" t="n">
+        <v>69</v>
+      </c>
       <c r="P16" s="12"/>
       <c r="Q16" s="12"/>
       <c r="R16" s="12"/>
@@ -1959,8 +1995,12 @@
       <c r="M18" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
+      <c r="N18" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="O18" s="12" t="n">
+        <v>83</v>
+      </c>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
       <c r="R18" s="12"/>
@@ -2024,8 +2064,12 @@
       <c r="M19" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
+      <c r="N19" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="O19" s="12" t="n">
+        <v>57</v>
+      </c>
       <c r="P19" s="12"/>
       <c r="Q19" s="12"/>
       <c r="R19" s="12"/>
@@ -2089,8 +2133,12 @@
       <c r="M20" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
+      <c r="N20" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="O20" s="12" t="n">
+        <v>57</v>
+      </c>
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
       <c r="R20" s="12"/>
@@ -2154,8 +2202,12 @@
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
+      <c r="N21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="P21" s="12"/>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
@@ -2260,8 +2312,12 @@
       <c r="M23" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
+      <c r="N23" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="O23" s="12" t="n">
+        <v>50</v>
+      </c>
       <c r="P23" s="12"/>
       <c r="Q23" s="12"/>
       <c r="R23" s="12"/>
@@ -2325,8 +2381,12 @@
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
+      <c r="N24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="P24" s="12"/>
       <c r="Q24" s="12"/>
       <c r="R24" s="12"/>
@@ -2395,7 +2455,7 @@
         <v>90</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2404,7 +2464,7 @@
       </c>
       <c r="C2" s="16" t="n">
         <f aca="false">MATCH(C1,บันทึกผล!$G$4:$U$4,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2473,11 +2533,11 @@
       </c>
       <c r="H5" s="20" t="n">
         <f aca="false">IF($C$2&lt;M5,0,IF($C$2&gt;=N5,100,ROUND(($C$2-M5+1)/(N5-M5+1)*100,0)))</f>
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="I5" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G6:INDEX(บันทึกผล!$G6:$U6,$C$2)),0)</f>
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="J5" s="20" t="n">
         <f aca="false">I5-H5</f>
@@ -2527,11 +2587,11 @@
       </c>
       <c r="H6" s="20" t="n">
         <f aca="false">IF($C$2&lt;M6,0,IF($C$2&gt;=N6,100,ROUND(($C$2-M6+1)/(N6-M6+1)*100,0)))</f>
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I6" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G7:INDEX(บันทึกผล!$G7:$U7,$C$2)),0)</f>
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="J6" s="20" t="n">
         <f aca="false">I6-H6</f>
@@ -2581,11 +2641,11 @@
       </c>
       <c r="H7" s="20" t="n">
         <f aca="false">IF($C$2&lt;M7,0,IF($C$2&gt;=N7,100,ROUND(($C$2-M7+1)/(N7-M7+1)*100,0)))</f>
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I7" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G8:INDEX(บันทึกผล!$G8:$U8,$C$2)),0)</f>
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="J7" s="20" t="n">
         <f aca="false">I7-H7</f>
@@ -2635,11 +2695,11 @@
       </c>
       <c r="H8" s="20" t="n">
         <f aca="false">IF($C$2&lt;M8,0,IF($C$2&gt;=N8,100,ROUND(($C$2-M8+1)/(N8-M8+1)*100,0)))</f>
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I8" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G10:INDEX(บันทึกผล!$G10:$U10,$C$2)),0)</f>
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="J8" s="20" t="n">
         <f aca="false">I8-H8</f>
@@ -2743,11 +2803,11 @@
       </c>
       <c r="H10" s="20" t="n">
         <f aca="false">IF($C$2&lt;M10,0,IF($C$2&gt;=N10,100,ROUND(($C$2-M10+1)/(N10-M10+1)*100,0)))</f>
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I10" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G12:INDEX(บันทึกผล!$G12:$U12,$C$2)),0)</f>
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="J10" s="20" t="n">
         <f aca="false">I10-H10</f>
@@ -2797,11 +2857,11 @@
       </c>
       <c r="H11" s="20" t="n">
         <f aca="false">IF($C$2&lt;M11,0,IF($C$2&gt;=N11,100,ROUND(($C$2-M11+1)/(N11-M11+1)*100,0)))</f>
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="I11" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G14:INDEX(บันทึกผล!$G14:$U14,$C$2)),0)</f>
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="J11" s="20" t="n">
         <f aca="false">I11-H11</f>
@@ -2851,11 +2911,11 @@
       </c>
       <c r="H12" s="20" t="n">
         <f aca="false">IF($C$2&lt;M12,0,IF($C$2&gt;=N12,100,ROUND(($C$2-M12+1)/(N12-M12+1)*100,0)))</f>
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="I12" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G15:INDEX(บันทึกผล!$G15:$U15,$C$2)),0)</f>
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="J12" s="20" t="n">
         <f aca="false">I12-H12</f>
@@ -2905,11 +2965,11 @@
       </c>
       <c r="H13" s="20" t="n">
         <f aca="false">IF($C$2&lt;M13,0,IF($C$2&gt;=N13,100,ROUND(($C$2-M13+1)/(N13-M13+1)*100,0)))</f>
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="I13" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G16:INDEX(บันทึกผล!$G16:$U16,$C$2)),0)</f>
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="J13" s="20" t="n">
         <f aca="false">I13-H13</f>
@@ -2959,11 +3019,11 @@
       </c>
       <c r="H14" s="20" t="n">
         <f aca="false">IF($C$2&lt;M14,0,IF($C$2&gt;=N14,100,ROUND(($C$2-M14+1)/(N14-M14+1)*100,0)))</f>
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="I14" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G18:INDEX(บันทึกผล!$G18:$U18,$C$2)),0)</f>
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="J14" s="20" t="n">
         <f aca="false">I14-H14</f>
@@ -3013,11 +3073,11 @@
       </c>
       <c r="H15" s="20" t="n">
         <f aca="false">IF($C$2&lt;M15,0,IF($C$2&gt;=N15,100,ROUND(($C$2-M15+1)/(N15-M15+1)*100,0)))</f>
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="I15" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G19:INDEX(บันทึกผล!$G19:$U19,$C$2)),0)</f>
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="J15" s="20" t="n">
         <f aca="false">I15-H15</f>
@@ -3067,11 +3127,11 @@
       </c>
       <c r="H16" s="20" t="n">
         <f aca="false">IF($C$2&lt;M16,0,IF($C$2&gt;=N16,100,ROUND(($C$2-M16+1)/(N16-M16+1)*100,0)))</f>
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="I16" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G20:INDEX(บันทึกผล!$G20:$U20,$C$2)),0)</f>
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="J16" s="20" t="n">
         <f aca="false">I16-H16</f>
@@ -3175,11 +3235,11 @@
       </c>
       <c r="H18" s="20" t="n">
         <f aca="false">IF($C$2&lt;M18,0,IF($C$2&gt;=N18,100,ROUND(($C$2-M18+1)/(N18-M18+1)*100,0)))</f>
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="I18" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G23:INDEX(บันทึกผล!$G23:$U23,$C$2)),0)</f>
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="J18" s="20" t="n">
         <f aca="false">I18-H18</f>
@@ -3280,11 +3340,11 @@
       </c>
       <c r="B23" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="1")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="1")*$D$5:$D$19),0)</f>
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="1")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="1")*$D$5:$D$19),0)</f>
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D23" s="24" t="n">
         <f aca="false">C23-B23</f>
@@ -3301,11 +3361,11 @@
       </c>
       <c r="B24" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="2")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="2")*$D$5:$D$19),0)</f>
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C24" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="2")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="2")*$D$5:$D$19),0)</f>
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D24" s="24" t="n">
         <f aca="false">C24-B24</f>
@@ -3322,11 +3382,11 @@
       </c>
       <c r="B25" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="3")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="3")*$D$5:$D$19),0)</f>
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C25" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="3")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="3")*$D$5:$D$19),0)</f>
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D25" s="24" t="n">
         <f aca="false">C25-B25</f>
@@ -3343,11 +3403,11 @@
       </c>
       <c r="B26" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="4")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="4")*$D$5:$D$19),0)</f>
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C26" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="4")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="4")*$D$5:$D$19),0)</f>
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D26" s="24" t="n">
         <f aca="false">C26-B26</f>
@@ -3364,11 +3424,11 @@
       </c>
       <c r="B27" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="5")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="5")*$D$5:$D$19),0)</f>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C27" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="5")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="5")*$D$5:$D$19),0)</f>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D27" s="24" t="n">
         <f aca="false">C27-B27</f>
@@ -3385,11 +3445,11 @@
       </c>
       <c r="B28" s="26" t="n">
         <f aca="false">ROUND(SUMPRODUCT($D$5:$D$19,$H$5:$H$19)/SUM($D$5:$D$19),0)</f>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C28" s="26" t="n">
         <f aca="false">ROUND(SUMPRODUCT($D$5:$D$19,$I$5:$I$19)/SUM($D$5:$D$19),0)</f>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D28" s="26" t="n">
         <f aca="false">C28-B28</f>

--- a/CP_2569_บันทึกผลจริง_template.xlsx
+++ b/CP_2569_บันทึกผลจริง_template.xlsx
@@ -1257,7 +1257,9 @@
       <c r="O6" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="P6" s="12"/>
+      <c r="P6" s="12" t="n">
+        <v>77</v>
+      </c>
       <c r="Q6" s="12"/>
       <c r="R6" s="12"/>
       <c r="S6" s="12"/>
@@ -1326,7 +1328,9 @@
       <c r="O7" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="P7" s="12"/>
+      <c r="P7" s="12" t="n">
+        <v>83</v>
+      </c>
       <c r="Q7" s="12"/>
       <c r="R7" s="12"/>
       <c r="S7" s="12"/>
@@ -1395,7 +1399,9 @@
       <c r="O8" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="P8" s="12"/>
+      <c r="P8" s="12" t="n">
+        <v>83</v>
+      </c>
       <c r="Q8" s="12"/>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
@@ -1505,7 +1511,9 @@
       <c r="O10" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="P10" s="12"/>
+      <c r="P10" s="12" t="n">
+        <v>83</v>
+      </c>
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
@@ -1574,7 +1582,9 @@
       <c r="O11" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="P11" s="12"/>
+      <c r="P11" s="12" t="n">
+        <v>100</v>
+      </c>
       <c r="Q11" s="12"/>
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
@@ -1643,7 +1653,9 @@
       <c r="O12" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="P12" s="12"/>
+      <c r="P12" s="12" t="n">
+        <v>83</v>
+      </c>
       <c r="Q12" s="12"/>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
@@ -1753,7 +1765,9 @@
       <c r="O14" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="P14" s="12"/>
+      <c r="P14" s="12" t="n">
+        <v>77</v>
+      </c>
       <c r="Q14" s="12"/>
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
@@ -1822,7 +1836,9 @@
       <c r="O15" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="P15" s="12"/>
+      <c r="P15" s="12" t="n">
+        <v>77</v>
+      </c>
       <c r="Q15" s="12"/>
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
@@ -1891,7 +1907,9 @@
       <c r="O16" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="P16" s="12"/>
+      <c r="P16" s="12" t="n">
+        <v>77</v>
+      </c>
       <c r="Q16" s="12"/>
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
@@ -2001,7 +2019,9 @@
       <c r="O18" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="P18" s="12"/>
+      <c r="P18" s="12" t="n">
+        <v>100</v>
+      </c>
       <c r="Q18" s="12"/>
       <c r="R18" s="12"/>
       <c r="S18" s="12"/>
@@ -2070,7 +2090,9 @@
       <c r="O19" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="P19" s="12"/>
+      <c r="P19" s="12" t="n">
+        <v>71</v>
+      </c>
       <c r="Q19" s="12"/>
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
@@ -2139,7 +2161,9 @@
       <c r="O20" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="P20" s="12"/>
+      <c r="P20" s="12" t="n">
+        <v>71</v>
+      </c>
       <c r="Q20" s="12"/>
       <c r="R20" s="12"/>
       <c r="S20" s="12"/>
@@ -2208,7 +2232,9 @@
       <c r="O21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P21" s="12"/>
+      <c r="P21" s="12" t="n">
+        <v>17</v>
+      </c>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
       <c r="S21" s="12"/>
@@ -2318,7 +2344,9 @@
       <c r="O23" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="P23" s="12"/>
+      <c r="P23" s="12" t="n">
+        <v>67</v>
+      </c>
       <c r="Q23" s="12"/>
       <c r="R23" s="12"/>
       <c r="S23" s="12"/>
@@ -2387,7 +2415,9 @@
       <c r="O24" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P24" s="12"/>
+      <c r="P24" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="Q24" s="12"/>
       <c r="R24" s="12"/>
       <c r="S24" s="12"/>
@@ -2455,7 +2485,7 @@
         <v>90</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2464,7 +2494,7 @@
       </c>
       <c r="C2" s="16" t="n">
         <f aca="false">MATCH(C1,บันทึกผล!$G$4:$U$4,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2533,11 +2563,11 @@
       </c>
       <c r="H5" s="20" t="n">
         <f aca="false">IF($C$2&lt;M5,0,IF($C$2&gt;=N5,100,ROUND(($C$2-M5+1)/(N5-M5+1)*100,0)))</f>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I5" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G6:INDEX(บันทึกผล!$G6:$U6,$C$2)),0)</f>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J5" s="20" t="n">
         <f aca="false">I5-H5</f>
@@ -2587,11 +2617,11 @@
       </c>
       <c r="H6" s="20" t="n">
         <f aca="false">IF($C$2&lt;M6,0,IF($C$2&gt;=N6,100,ROUND(($C$2-M6+1)/(N6-M6+1)*100,0)))</f>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I6" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G7:INDEX(บันทึกผล!$G7:$U7,$C$2)),0)</f>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J6" s="20" t="n">
         <f aca="false">I6-H6</f>
@@ -2641,11 +2671,11 @@
       </c>
       <c r="H7" s="20" t="n">
         <f aca="false">IF($C$2&lt;M7,0,IF($C$2&gt;=N7,100,ROUND(($C$2-M7+1)/(N7-M7+1)*100,0)))</f>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I7" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G8:INDEX(บันทึกผล!$G8:$U8,$C$2)),0)</f>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J7" s="20" t="n">
         <f aca="false">I7-H7</f>
@@ -2695,11 +2725,11 @@
       </c>
       <c r="H8" s="20" t="n">
         <f aca="false">IF($C$2&lt;M8,0,IF($C$2&gt;=N8,100,ROUND(($C$2-M8+1)/(N8-M8+1)*100,0)))</f>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I8" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G10:INDEX(บันทึกผล!$G10:$U10,$C$2)),0)</f>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J8" s="20" t="n">
         <f aca="false">I8-H8</f>
@@ -2803,11 +2833,11 @@
       </c>
       <c r="H10" s="20" t="n">
         <f aca="false">IF($C$2&lt;M10,0,IF($C$2&gt;=N10,100,ROUND(($C$2-M10+1)/(N10-M10+1)*100,0)))</f>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I10" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G12:INDEX(บันทึกผล!$G12:$U12,$C$2)),0)</f>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J10" s="20" t="n">
         <f aca="false">I10-H10</f>
@@ -2857,11 +2887,11 @@
       </c>
       <c r="H11" s="20" t="n">
         <f aca="false">IF($C$2&lt;M11,0,IF($C$2&gt;=N11,100,ROUND(($C$2-M11+1)/(N11-M11+1)*100,0)))</f>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I11" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G14:INDEX(บันทึกผล!$G14:$U14,$C$2)),0)</f>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J11" s="20" t="n">
         <f aca="false">I11-H11</f>
@@ -2911,11 +2941,11 @@
       </c>
       <c r="H12" s="20" t="n">
         <f aca="false">IF($C$2&lt;M12,0,IF($C$2&gt;=N12,100,ROUND(($C$2-M12+1)/(N12-M12+1)*100,0)))</f>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I12" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G15:INDEX(บันทึกผล!$G15:$U15,$C$2)),0)</f>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J12" s="20" t="n">
         <f aca="false">I12-H12</f>
@@ -2965,11 +2995,11 @@
       </c>
       <c r="H13" s="20" t="n">
         <f aca="false">IF($C$2&lt;M13,0,IF($C$2&gt;=N13,100,ROUND(($C$2-M13+1)/(N13-M13+1)*100,0)))</f>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I13" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G16:INDEX(บันทึกผล!$G16:$U16,$C$2)),0)</f>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J13" s="20" t="n">
         <f aca="false">I13-H13</f>
@@ -3019,11 +3049,11 @@
       </c>
       <c r="H14" s="20" t="n">
         <f aca="false">IF($C$2&lt;M14,0,IF($C$2&gt;=N14,100,ROUND(($C$2-M14+1)/(N14-M14+1)*100,0)))</f>
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="I14" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G18:INDEX(บันทึกผล!$G18:$U18,$C$2)),0)</f>
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="J14" s="20" t="n">
         <f aca="false">I14-H14</f>
@@ -3073,11 +3103,11 @@
       </c>
       <c r="H15" s="20" t="n">
         <f aca="false">IF($C$2&lt;M15,0,IF($C$2&gt;=N15,100,ROUND(($C$2-M15+1)/(N15-M15+1)*100,0)))</f>
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="I15" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G19:INDEX(บันทึกผล!$G19:$U19,$C$2)),0)</f>
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="J15" s="20" t="n">
         <f aca="false">I15-H15</f>
@@ -3127,11 +3157,11 @@
       </c>
       <c r="H16" s="20" t="n">
         <f aca="false">IF($C$2&lt;M16,0,IF($C$2&gt;=N16,100,ROUND(($C$2-M16+1)/(N16-M16+1)*100,0)))</f>
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="I16" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G20:INDEX(บันทึกผล!$G20:$U20,$C$2)),0)</f>
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="J16" s="20" t="n">
         <f aca="false">I16-H16</f>
@@ -3181,11 +3211,11 @@
       </c>
       <c r="H17" s="20" t="n">
         <f aca="false">IF($C$2&lt;M17,0,IF($C$2&gt;=N17,100,ROUND(($C$2-M17+1)/(N17-M17+1)*100,0)))</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I17" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G21:INDEX(บันทึกผล!$G21:$U21,$C$2)),0)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J17" s="20" t="n">
         <f aca="false">I17-H17</f>
@@ -3193,7 +3223,7 @@
       </c>
       <c r="K17" s="18" t="str">
         <f aca="false">IF(H17=0,"รอกำหนด",IF(I17&gt;=H17,"ตามแผน",IF(H17-I17&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
-        <v>รอกำหนด</v>
+        <v>ตามแผน</v>
       </c>
       <c r="M17" s="1" t="n">
         <f aca="false">MATCH(E17,บันทึกผล!$G$4:$U$4,0)</f>
@@ -3235,11 +3265,11 @@
       </c>
       <c r="H18" s="20" t="n">
         <f aca="false">IF($C$2&lt;M18,0,IF($C$2&gt;=N18,100,ROUND(($C$2-M18+1)/(N18-M18+1)*100,0)))</f>
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="I18" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G23:INDEX(บันทึกผล!$G23:$U23,$C$2)),0)</f>
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="J18" s="20" t="n">
         <f aca="false">I18-H18</f>
@@ -3340,11 +3370,11 @@
       </c>
       <c r="B23" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="1")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="1")*$D$5:$D$19),0)</f>
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="1")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="1")*$D$5:$D$19),0)</f>
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D23" s="24" t="n">
         <f aca="false">C23-B23</f>
@@ -3361,11 +3391,11 @@
       </c>
       <c r="B24" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="2")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="2")*$D$5:$D$19),0)</f>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C24" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="2")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="2")*$D$5:$D$19),0)</f>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D24" s="24" t="n">
         <f aca="false">C24-B24</f>
@@ -3382,11 +3412,11 @@
       </c>
       <c r="B25" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="3")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="3")*$D$5:$D$19),0)</f>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C25" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="3")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="3")*$D$5:$D$19),0)</f>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D25" s="24" t="n">
         <f aca="false">C25-B25</f>
@@ -3403,11 +3433,11 @@
       </c>
       <c r="B26" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="4")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="4")*$D$5:$D$19),0)</f>
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C26" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="4")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="4")*$D$5:$D$19),0)</f>
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D26" s="24" t="n">
         <f aca="false">C26-B26</f>
@@ -3424,11 +3454,11 @@
       </c>
       <c r="B27" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="5")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="5")*$D$5:$D$19),0)</f>
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C27" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="5")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="5")*$D$5:$D$19),0)</f>
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D27" s="24" t="n">
         <f aca="false">C27-B27</f>
@@ -3445,11 +3475,11 @@
       </c>
       <c r="B28" s="26" t="n">
         <f aca="false">ROUND(SUMPRODUCT($D$5:$D$19,$H$5:$H$19)/SUM($D$5:$D$19),0)</f>
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C28" s="26" t="n">
         <f aca="false">ROUND(SUMPRODUCT($D$5:$D$19,$I$5:$I$19)/SUM($D$5:$D$19),0)</f>
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D28" s="26" t="n">
         <f aca="false">C28-B28</f>
